--- a/results/job_matches_2026-03-02.xlsx
+++ b/results/job_matches_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Databricks Architect &amp; Developer</t>
+          <t>DevOps Engineer (Linux)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kollasoft Inc</t>
+          <t>Quantifind</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.3</v>
+        <v>11.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Databricks, Spark, PySpark</t>
+          <t>AWS, Hadoop, Scala, PostgreSQL, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961f7719b1e41e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=87617613276c990f</t>
         </is>
       </c>
     </row>
@@ -567,76 +567,6 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a677917152c7ba4a</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24e1bdbed934be1c</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c61f3a7795625e6</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-02.xlsx
+++ b/results/job_matches_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,47 +468,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Linux)</t>
+          <t>Databricks Architect &amp; Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Quantifind</t>
+          <t>Kollasoft Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11.1</v>
+        <v>15.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Scala, PostgreSQL, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87617613276c990f</t>
+          <t>https://www.indeed.com/viewjob?jk=961f7719b1e41e9a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>DevOps Engineer (Linux)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Quantifind</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -521,50 +521,85 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>AWS, Hadoop, Scala, PostgreSQL, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5096db1f348c8e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=87617613276c990f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Senior Engineer - Java</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5096db1f348c8e4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Project Delivery Specialist - Sr. API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Deloitte</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>10.4</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a677917152c7ba4a</t>
         </is>

--- a/results/job_matches_2026-03-02.xlsx
+++ b/results/job_matches_2026-03-02.xlsx
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Linux)</t>
+          <t>Systems Engineering - Senior Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quantifind</t>
+          <t>simple construction</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Flushing, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Scala, PostgreSQL, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87617613276c990f</t>
+          <t>https://www.indeed.com/viewjob?jk=6722fcc4d5da627b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>DevOps Engineer (Linux)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Quantifind</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -556,52 +556,52 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>AWS, Hadoop, Scala, PostgreSQL, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5096db1f348c8e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=87617613276c990f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Project Delivery Specialist - Sr. API &amp; Azure DevOps Developer - Remote</t>
+          <t>Senior Engineer - Java</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a677917152c7ba4a</t>
+          <t>https://www.indeed.com/viewjob?jk=5096db1f348c8e4b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-02.xlsx
+++ b/results/job_matches_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Systems Engineering - Senior Engineer</t>
+          <t>DevOps Engineer (Linux)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>simple construction</t>
+          <t>Quantifind</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Flushing, MI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Hadoop, Scala, PostgreSQL, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6722fcc4d5da627b</t>
+          <t>https://www.indeed.com/viewjob?jk=87617613276c990f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Linux)</t>
+          <t>Senior Engineer - Java</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quantifind</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -556,50 +556,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Scala, PostgreSQL, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87617613276c990f</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5096db1f348c8e4b</t>
         </is>

--- a/results/job_matches_2026-03-02.xlsx
+++ b/results/job_matches_2026-03-02.xlsx
@@ -468,47 +468,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Databricks Architect &amp; Developer</t>
+          <t>DevOps Engineer (Linux)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kollasoft Inc</t>
+          <t>Quantifind</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.3</v>
+        <v>11.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Databricks, Spark, PySpark</t>
+          <t>AWS, Hadoop, Scala, PostgreSQL, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961f7719b1e41e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=87617613276c990f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Linux)</t>
+          <t>Senior Engineer - Java</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quantifind</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -521,52 +521,52 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Scala, PostgreSQL, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87617613276c990f</t>
+          <t>https://www.indeed.com/viewjob?jk=5096db1f348c8e4b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ISHIR</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5096db1f348c8e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-02.xlsx
+++ b/results/job_matches_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Linux)</t>
+          <t>Data Architect – Health Care Payer Domain</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Quantifind</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Scala, PostgreSQL, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, HDFS, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,77 +496,182 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87617613276c990f</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9633621ca2925b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5096db1f348c8e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=e1534e35cf264fdf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>DevOps Engineer (Linux)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Quantifind</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AWS, Hadoop, Scala, PostgreSQL, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87617613276c990f</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5096db1f348c8e4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Forward Deployed Engineer</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>ISHIR</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Dallas, TX, US USA</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D6" t="n">
         <v>10.4</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Credify Services</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5b23147f1037240</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-02.xlsx
+++ b/results/job_matches_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Architect – Health Care Payer Domain</t>
+          <t>Data Analyst Intern (Advanced SQL / Python / Data Engineering Focus)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>Machinery Marketing Inter</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.9</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, HDFS, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9633621ca2925b</t>
+          <t>https://www.indeed.com/viewjob?jk=4f2663b45d759cf1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.8</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1534e35cf264fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=8385283e2d310884</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Linux)</t>
+          <t>Kafka Streaming Analyst</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quantifind</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Scala, PostgreSQL, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87617613276c990f</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d30813f5ba8de3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>Senior Kafka Migration Specialist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, HBase, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5096db1f348c8e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=10bf1f673e41ef2e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,40 +636,600 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=e4308f77f38286dd</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Data Architect – Health Care Payer Domain</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Digital Dhara LLC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, HDFS, Spark, Scala, Oracle, SQL Server</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb9633621ca2925b</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Java Full Stack Engineer - Professional</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hexaware Technologies</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75a593062a046b0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Kafka Microservices Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MLOps Specialist</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Domino's</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ann Arbor, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Kafka Migration Specialist</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Kafka API Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, NoSQL, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1534e35cf264fdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Kafka Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Kafka DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Streaming Data</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DevOps Engineer (Linux)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Quantifind</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, Hadoop, Scala, PostgreSQL, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87617613276c990f</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5096db1f348c8e4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Kafka Schema Registry Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ISHIR</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Kafka Implementation Consultant</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Kafka API Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Senior Software Engineer</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Credify Services</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D23" t="n">
         <v>10.4</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Docker, Git</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f5b23147f1037240</t>
         </is>

--- a/results/job_matches_2026-03-02.xlsx
+++ b/results/job_matches_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Analyst Intern (Advanced SQL / Python / Data Engineering Focus)</t>
+          <t>Full Stack Engineer (React + Node.js)-3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Machinery Marketing Inter</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f2663b45d759cf1</t>
+          <t>https://www.indeed.com/viewjob?jk=8b7d8b7b5770a45b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Data Analyst Intern (Advanced SQL / Python / Data Engineering Focus)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Machinery Marketing Inter</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8385283e2d310884</t>
+          <t>https://www.indeed.com/viewjob?jk=4f2663b45d759cf1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kafka Streaming Analyst</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, API Gateway, IAM</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d30813f5ba8de3</t>
+          <t>https://www.indeed.com/viewjob?jk=8385283e2d310884</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Kafka Migration Specialist</t>
+          <t>Kafka Streaming Analyst</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.9</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, HBase, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10bf1f673e41ef2e</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d30813f5ba8de3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Node JS Architect – R01560914</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4308f77f38286dd</t>
+          <t>https://www.indeed.com/viewjob?jk=cfa80a7ee6afe55d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Architect – Health Care Payer Domain</t>
+          <t>Software Engineering Senior Advisors- Hybrid</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, HDFS, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,49 +671,49 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9633621ca2925b</t>
+          <t>https://www.indeed.com/viewjob?jk=b9948a6eb09905fb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer - Professional</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75a593062a046b0c</t>
+          <t>https://www.indeed.com/viewjob?jk=61410e9fc055bb62</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kafka Microservices Engineer</t>
+          <t>Senior Kafka Migration Specialist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, HBase, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=10bf1f673e41ef2e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MLOps Specialist</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=e4308f77f38286dd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Kafka Migration Specialist</t>
+          <t>Data Architect – Health Care Payer Domain</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, HDFS, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9633621ca2925b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
+          <t>https://www.indeed.com/viewjob?jk=3f42ee3004396e21</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Nuve Controls LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1534e35cf264fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Kafka Integration Engineer</t>
+          <t>Solutions Architect - AI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Robots &amp; Pencils</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=e9e0f4d3981383ee</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Kafka DevOps Engineer</t>
+          <t>Java Full Stack Engineer - Professional</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
+          <t>https://www.indeed.com/viewjob?jk=75a593062a046b0c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Sr. SQL Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Walton Hills, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
+          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Linux)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Quantifind</t>
+          <t>OmniTrust Technologies</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Scala, PostgreSQL, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow</t>
+          <t>AWS, S3, SNS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87617613276c990f</t>
+          <t>https://www.indeed.com/viewjob?jk=861d98ce8ccd9dd9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5096db1f348c8e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=9c635f2175e2d81b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fusion Risk Management</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
+          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Kafka Microservices Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kafka Implementation Consultant</t>
+          <t>MLOps Specialist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
+          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Senior Kafka Migration Specialist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,42 +1196,427 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
+          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Kafka API Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Kafka Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Kafka DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Streaming Data</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DevOps Engineer (Linux)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Quantifind</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, Hadoop, Scala, PostgreSQL, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87617613276c990f</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5096db1f348c8e4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Kafka Schema Registry Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ISHIR</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Kafka Implementation Consultant</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Kafka API Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Senior Software Engineer</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Credify Services</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D33" t="n">
         <v>10.4</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Docker, Git</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f5b23147f1037240</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Azure Databricks Architect-5</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Mahwah, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ddae10e310d8abb2</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-02.xlsx
+++ b/results/job_matches_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Kafka Migration Specialist</t>
+          <t>Senior Data Platform SIEM Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, HBase, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Kinesis, S3, RDS, Azure, Event Hubs, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10bf1f673e41ef2e</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fef1f451ba88d8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Senior Kafka Migration Specialist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, HBase, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4308f77f38286dd</t>
+          <t>https://www.indeed.com/viewjob?jk=10bf1f673e41ef2e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Architect – Health Care Payer Domain</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, HDFS, Spark, Scala, Oracle, SQL Server</t>
+          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9633621ca2925b</t>
+          <t>https://www.indeed.com/viewjob?jk=e4308f77f38286dd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data Architect – Health Care Payer Domain</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, HDFS, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f42ee3004396e21</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9633621ca2925b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nuve Controls LLC</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
+          <t>https://www.indeed.com/viewjob?jk=3f42ee3004396e21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Solutions Architect - AI</t>
+          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Robots &amp; Pencils</t>
+          <t>Nuve Controls LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, API Gateway, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9e0f4d3981383ee</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer - Professional</t>
+          <t>Sr. Palantir Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>A2R Global Private Limited</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75a593062a046b0c</t>
+          <t>https://www.indeed.com/viewjob?jk=d3b46185a95c7ee3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. SQL Developer</t>
+          <t>Solutions Architect - AI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Robots &amp; Pencils</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Walton Hills, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
+          <t>https://www.indeed.com/viewjob?jk=e9e0f4d3981383ee</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java Full Stack Engineer - Professional</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>OmniTrust Technologies</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861d98ce8ccd9dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=75a593062a046b0c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Sr. SQL Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Walton Hills, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c635f2175e2d81b</t>
+          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fusion Risk Management</t>
+          <t>OmniTrust Technologies</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, SNS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
+          <t>https://www.indeed.com/viewjob?jk=861d98ce8ccd9dd9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kafka Microservices Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=9c635f2175e2d81b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MLOps Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Fusion Risk Management</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Kafka Migration Specialist</t>
+          <t>Kafka Microservices Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>MLOps Specialist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
+          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Kafka Integration Engineer</t>
+          <t>Senior Kafka Migration Specialist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Kafka DevOps Engineer</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1287,11 +1287,11 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
+          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Kafka Integration Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Linux)</t>
+          <t>Senior Kafka DevOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Quantifind</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Scala, PostgreSQL, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow</t>
+          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87617613276c990f</t>
+          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5096db1f348c8e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>DevOps Engineer (Linux)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Quantifind</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Hadoop, Scala, PostgreSQL, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,49 +1441,49 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
+          <t>https://www.indeed.com/viewjob?jk=87617613276c990f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Engineer - Java</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=5096db1f348c8e4b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kafka Implementation Consultant</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1497,11 +1497,11 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
+          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ISHIR</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
+          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Kafka Implementation Consultant</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Credify Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Docker, Git</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b23147f1037240</t>
+          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-5</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,15 +1606,85 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Credify Services</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5b23147f1037240</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Azure Databricks Architect-5</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Mahwah, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ddae10e310d8abb2</t>
         </is>

--- a/results/job_matches_2026-03-02.xlsx
+++ b/results/job_matches_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)-3</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>OmniTrust Technologies</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>22.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, RDS, Databricks, Medallion Architecture, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b7d8b7b5770a45b</t>
+          <t>https://www.indeed.com/viewjob?jk=d62af133e60ea749</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Analyst Intern (Advanced SQL / Python / Data Engineering Focus)</t>
+          <t>Data Engineer - Archimedes</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Machinery Marketing Inter</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,77 +521,77 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f2663b45d759cf1</t>
+          <t>https://www.indeed.com/viewjob?jk=cc2b4e99dfcfee5e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Data Engineer - Archimedes</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8385283e2d310884</t>
+          <t>https://www.indeed.com/viewjob?jk=79098e07510f4870</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kafka Streaming Analyst</t>
+          <t>Full Stack Engineer (React + Node.js)-3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, API Gateway, IAM</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d30813f5ba8de3</t>
+          <t>https://www.indeed.com/viewjob?jk=8b7d8b7b5770a45b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Node JS Architect – R01560914</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfa80a7ee6afe55d</t>
+          <t>https://www.indeed.com/viewjob?jk=8385283e2d310884</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisors- Hybrid</t>
+          <t>Kafka Streaming Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9948a6eb09905fb</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d30813f5ba8de3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Node JS Architect – R01560914</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61410e9fc055bb62</t>
+          <t>https://www.indeed.com/viewjob?jk=cfa80a7ee6afe55d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Platform SIEM Engineer</t>
+          <t>Software Engineering Senior Advisors- Hybrid</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Azure, Event Hubs, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fef1f451ba88d8</t>
+          <t>https://www.indeed.com/viewjob?jk=b9948a6eb09905fb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Kafka Migration Specialist</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>reveleer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, HBase, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10bf1f673e41ef2e</t>
+          <t>https://www.indeed.com/viewjob?jk=9f77843ee754ca2e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Senior Data Platform SIEM Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Kinesis, S3, RDS, Azure, Event Hubs, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4308f77f38286dd</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fef1f451ba88d8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Architect – Health Care Payer Domain</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, HDFS, Spark, Scala, Oracle, SQL Server</t>
+          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9633621ca2925b</t>
+          <t>https://www.indeed.com/viewjob?jk=e4308f77f38286dd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data Architect – Health Care Payer Domain</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, HDFS, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f42ee3004396e21</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9633621ca2925b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
+          <t>Sr. Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nuve Controls LLC</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
+          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Palantir Architect</t>
+          <t>Senior Kafka Migration Specialist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A2R Global Private Limited</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, HBase, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3b46185a95c7ee3</t>
+          <t>https://www.indeed.com/viewjob?jk=10bf1f673e41ef2e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Solutions Architect - AI</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Robots &amp; Pencils</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, API Gateway, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9e0f4d3981383ee</t>
+          <t>https://www.indeed.com/viewjob?jk=3f42ee3004396e21</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer - Professional</t>
+          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>Nuve Controls LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,42 +1021,42 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75a593062a046b0c</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. SQL Developer</t>
+          <t>Solutions Architect - AI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Robots &amp; Pencils</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Walton Hills, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
+          <t>https://www.indeed.com/viewjob?jk=e9e0f4d3981383ee</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Sr. SQL Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Walton Hills, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,29 +1116,29 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c635f2175e2d81b</t>
+          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Full Stack Engineer - Professional</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fusion Risk Management</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1147,11 +1147,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
+          <t>https://www.indeed.com/viewjob?jk=75a593062a046b0c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kafka Microservices Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=9c635f2175e2d81b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MLOps Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Fusion Risk Management</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Kafka Migration Specialist</t>
+          <t>Kafka Microservices Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>MLOps Specialist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
+          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Kafka Integration Engineer</t>
+          <t>Senior Kafka Migration Specialist</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Kafka DevOps Engineer</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1357,11 +1357,11 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
+          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>VytlOne</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
+          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Linux)</t>
+          <t>Sr Engineer - Interactive Compute</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Quantifind</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Scala, PostgreSQL, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow</t>
+          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87617613276c990f</t>
+          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>Senior Kafka Integration Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,24 +1466,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5096db1f348c8e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Senior Kafka DevOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
+          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kafka Implementation Consultant</t>
+          <t>DevOps Engineer (Linux)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Quantifind</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, Hadoop, Scala, PostgreSQL, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
+          <t>https://www.indeed.com/viewjob?jk=87617613276c990f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Senior Engineer - Java</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
+          <t>https://www.indeed.com/viewjob?jk=5096db1f348c8e4b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Credify Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Docker, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b23147f1037240</t>
+          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-5</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>ISHIR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,157 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Azure Databricks Architect-5</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Mahwah, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ddae10e310d8abb2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Kafka Implementation Consultant</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Credify Services</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5b23147f1037240</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Kafka API Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-02.xlsx
+++ b/results/job_matches_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Senior Cloud DevOps Engineer (Azure &amp; AWS)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
+          <t>AWS, Glue, ECS, IAM, RDS, Azure, Data Factory, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8385283e2d310884</t>
+          <t>https://www.indeed.com/viewjob?jk=30ad4f76b32130ff</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kafka Streaming Analyst</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, API Gateway, IAM</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d30813f5ba8de3</t>
+          <t>https://www.indeed.com/viewjob?jk=8385283e2d310884</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Node JS Architect – R01560914</t>
+          <t>Kafka Streaming Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfa80a7ee6afe55d</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d30813f5ba8de3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineering Senior Advisors- Hybrid</t>
+          <t>Node JS Architect – R01560914</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9948a6eb09905fb</t>
+          <t>https://www.indeed.com/viewjob?jk=cfa80a7ee6afe55d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer (Spark | Hadoop | Apache Ozone), Berkeley Heights, NJ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>reveleer</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f77843ee754ca2e</t>
+          <t>https://www.indeed.com/viewjob?jk=1241769a525bbecb</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Platform SIEM Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>reveleer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Azure, Event Hubs, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fef1f451ba88d8</t>
+          <t>https://www.indeed.com/viewjob?jk=9f77843ee754ca2e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Senior Data Platform SIEM Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Kinesis, S3, RDS, Azure, Event Hubs, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4308f77f38286dd</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fef1f451ba88d8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Architect – Health Care Payer Domain</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, HDFS, Spark, Scala, Oracle, SQL Server</t>
+          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9633621ca2925b</t>
+          <t>https://www.indeed.com/viewjob?jk=e4308f77f38286dd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Machine Learning</t>
+          <t>Data Architect – Health Care Payer Domain</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, HDFS, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9633621ca2925b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Kafka Migration Specialist</t>
+          <t>Sr. Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, HBase, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10bf1f673e41ef2e</t>
+          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Kafka Migration Specialist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, HBase, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f42ee3004396e21</t>
+          <t>https://www.indeed.com/viewjob?jk=10bf1f673e41ef2e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
+          <t>Sr. ServiceNOW (DPR) Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nuve Controls LLC</t>
+          <t>XomegaIT Inc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
+          <t>https://www.indeed.com/viewjob?jk=3a18d71c9677d86f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Solutions Architect - AI</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Robots &amp; Pencils</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, API Gateway, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9e0f4d3981383ee</t>
+          <t>https://www.indeed.com/viewjob?jk=3f42ee3004396e21</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OmniTrust Technologies</t>
+          <t>Nuve Controls LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861d98ce8ccd9dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. SQL Developer</t>
+          <t>Solutions Architect - AI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Robots &amp; Pencils</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Walton Hills, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
+          <t>https://www.indeed.com/viewjob?jk=e9e0f4d3981383ee</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer - Professional</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>OmniTrust Technologies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, S3, SNS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75a593062a046b0c</t>
+          <t>https://www.indeed.com/viewjob?jk=861d98ce8ccd9dd9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Software Engineer II - AI/ML OPS Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c635f2175e2d81b</t>
+          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - onsite Dallas or NYC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fusion Risk Management</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,67 +1231,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
+          <t>https://www.indeed.com/viewjob?jk=1973f445d0cd1f85</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kafka Microservices Engineer</t>
+          <t>Sr. SQL Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Walton Hills, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MLOps Specialist</t>
+          <t>Java Full Stack Engineer - Professional</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=75a593062a046b0c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Kafka Migration Specialist</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Field Tech Services LTD</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=66ccf1b5ae0c7999</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
+          <t>https://www.indeed.com/viewjob?jk=9c635f2175e2d81b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VytlOne</t>
+          <t>Fusion Risk Management</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
+          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Engineer - Interactive Compute</t>
+          <t>Kafka Microservices Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
+          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Kafka Integration Engineer</t>
+          <t>MLOps Specialist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Kafka DevOps Engineer</t>
+          <t>Senior Kafka Migration Specialist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1497,11 +1497,11 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
+          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1532,11 +1532,11 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
+          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Linux)</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Quantifind</t>
+          <t>Ossium Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Scala, PostgreSQL, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,102 +1581,102 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87617613276c990f</t>
+          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5096db1f348c8e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>VytlOne</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
+          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>MLOps Engineer - ML Platform</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-5</t>
+          <t>Sr Engineer - Interactive Compute</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,14 +1721,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddae10e310d8abb2</t>
+          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kafka Implementation Consultant</t>
+          <t>Senior Kafka Integration Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1742,11 +1742,11 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Kafka DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Credify Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Docker, Git</t>
+          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,42 +1791,497 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b23147f1037240</t>
+          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Streaming Data</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>DevOps Engineer (Linux)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Quantifind</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, Hadoop, Scala, PostgreSQL, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87617613276c990f</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5096db1f348c8e4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Kafka Schema Registry Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Credit Karma</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Azure Databricks Architect-5</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Mahwah, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ddae10e310d8abb2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Kafka Implementation Consultant</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Credify Services</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5b23147f1037240</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>Kafka API Engineer</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Openkyber</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>AK, US USA</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D51" t="n">
         <v>10.4</v>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ISHIR</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Machine Learning Software Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48d779cadb2f27d6</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-02.xlsx
+++ b/results/job_matches_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,25 +713,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Node JS Architect – R01560914</t>
+          <t>FinOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfa80a7ee6afe55d</t>
+          <t>https://www.indeed.com/viewjob?jk=53b079e799b7b598</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer (Spark | Hadoop | Apache Ozone), Berkeley Heights, NJ</t>
+          <t>Sr. Data Engineer - Monetization &amp; Experimentation</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>RedCloud Consulting</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark</t>
+          <t>AWS, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1241769a525bbecb</t>
+          <t>https://www.indeed.com/viewjob?jk=25c4ec5f1d13bace</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Node JS Architect – R01560914</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>reveleer</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f77843ee754ca2e</t>
+          <t>https://www.indeed.com/viewjob?jk=cfa80a7ee6afe55d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Platform SIEM Engineer</t>
+          <t>Data Engineer (Spark | Hadoop | Apache Ozone), Berkeley Heights, NJ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Azure, Event Hubs, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fef1f451ba88d8</t>
+          <t>https://www.indeed.com/viewjob?jk=1241769a525bbecb</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>reveleer</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4308f77f38286dd</t>
+          <t>https://www.indeed.com/viewjob?jk=9f77843ee754ca2e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Architect – Health Care Payer Domain</t>
+          <t>Sr. Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, HDFS, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9633621ca2925b</t>
+          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Machine Learning</t>
+          <t>Senior Data Platform SIEM Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
+          <t>AWS, Kinesis, S3, RDS, Azure, Event Hubs, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fef1f451ba88d8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Kafka Migration Specialist</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, HBase, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10bf1f673e41ef2e</t>
+          <t>https://www.indeed.com/viewjob?jk=e4308f77f38286dd</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. ServiceNOW (DPR) Developer</t>
+          <t>Data Architect – Health Care Payer Domain</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>XomegaIT Inc</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, HDFS, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a18d71c9677d86f</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9633621ca2925b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Sr. ServiceNOW (DPR) Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>XomegaIT Inc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f42ee3004396e21</t>
+          <t>https://www.indeed.com/viewjob?jk=3a18d71c9677d86f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nuve Controls LLC</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
+          <t>https://www.indeed.com/viewjob?jk=3f42ee3004396e21</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Solutions Architect - AI</t>
+          <t>Senior Kafka Migration Specialist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Robots &amp; Pencils</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, API Gateway, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, HBase, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9e0f4d3981383ee</t>
+          <t>https://www.indeed.com/viewjob?jk=10bf1f673e41ef2e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>OmniTrust Technologies</t>
+          <t>Nuve Controls LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861d98ce8ccd9dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML OPS Engineer</t>
+          <t>Solutions Architect - AI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Robots &amp; Pencils</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
+          <t>https://www.indeed.com/viewjob?jk=e9e0f4d3981383ee</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - onsite Dallas or NYC</t>
+          <t>Child Support -Senior Full Stack AI/Java Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,59 +1231,59 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1973f445d0cd1f85</t>
+          <t>https://www.indeed.com/viewjob?jk=052ff8fd2f21f73c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. SQL Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>OmniTrust Technologies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Walton Hills, OH, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, S3, SNS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
+          <t>https://www.indeed.com/viewjob?jk=861d98ce8ccd9dd9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer - Professional</t>
+          <t>Software Engineer II - AI/ML OPS Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75a593062a046b0c</t>
+          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Senior Software Engineer - onsite Dallas or NYC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Field Tech Services LTD</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66ccf1b5ae0c7999</t>
+          <t>https://www.indeed.com/viewjob?jk=1973f445d0cd1f85</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Sr. SQL Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Walton Hills, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c635f2175e2d81b</t>
+          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fusion Risk Management</t>
+          <t>Field Tech Services LTD</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
+          <t>https://www.indeed.com/viewjob?jk=66ccf1b5ae0c7999</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kafka Microservices Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=9c635f2175e2d81b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MLOps Specialist</t>
+          <t>Java Full Stack Engineer - Professional</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=75a593062a046b0c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Kafka Migration Specialist</t>
+          <t>Kafka Microservices Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fusion Risk Management</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
+          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>MLOps Specialist</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>VytlOne</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,42 +1641,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
+          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MLOps Engineer - ML Platform</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,49 +1686,49 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
+          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Engineer - Interactive Compute</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>VytlOne</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
+          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Kafka Integration Engineer</t>
+          <t>Senior Kafka Migration Specialist</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1742,11 +1742,11 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
+          <t>MLOps Engineer - ML Platform</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
+          <t>Sr Engineer - Interactive Compute</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,14 +1966,14 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
+          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Senior Kafka Integration Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-5</t>
+          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,14 +2071,14 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddae10e310d8abb2</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kafka Implementation Consultant</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2092,11 +2092,11 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
+          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Credify Services</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b23147f1037240</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>ISHIR</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
+          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Azure Databricks Architect-5</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Mahwah, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=ddae10e310d8abb2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Machine Learning Software Engineer</t>
+          <t>Kafka Implementation Consultant</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,15 +2271,120 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Credify Services</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5b23147f1037240</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Kafka API Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Machine Learning Software Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>AWS, Azure, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=48d779cadb2f27d6</t>
         </is>

--- a/results/job_matches_2026-03-02.xlsx
+++ b/results/job_matches_2026-03-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kafka Streaming Analyst</t>
+          <t>FinOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, API Gateway, IAM</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d30813f5ba8de3</t>
+          <t>https://www.indeed.com/viewjob?jk=53b079e799b7b598</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FinOps Engineer</t>
+          <t>Senior Data Engineer, ACVMax</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>ACV Auctions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53b079e799b7b598</t>
+          <t>https://www.indeed.com/viewjob?jk=a05a21e755f84f81</t>
         </is>
       </c>
     </row>
@@ -783,25 +783,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Node JS Architect – R01560914</t>
+          <t>Data Engineer (Spark | Hadoop | Apache Ozone), Berkeley Heights, NJ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,54 +811,54 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfa80a7ee6afe55d</t>
+          <t>https://www.indeed.com/viewjob?jk=1241769a525bbecb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer (Spark | Hadoop | Apache Ozone), Berkeley Heights, NJ</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>reveleer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1241769a525bbecb</t>
+          <t>https://www.indeed.com/viewjob?jk=9f77843ee754ca2e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>reveleer</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f77843ee754ca2e</t>
+          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Machine Learning</t>
+          <t>Sr. ServiceNOW (DPR) Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>XomegaIT Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Dask, Snowflake, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9938efe3610b0fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=3a18d71c9677d86f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Platform SIEM Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Azure, Event Hubs, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fef1f451ba88d8</t>
+          <t>https://www.indeed.com/viewjob?jk=3f42ee3004396e21</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Nuve Controls LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tustin, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4308f77f38286dd</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Architect – Health Care Payer Domain</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, HDFS, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Redshift, RDS, GCP, Hive, Oozie, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9633621ca2925b</t>
+          <t>https://www.indeed.com/viewjob?jk=34d768a204f4d158</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. ServiceNOW (DPR) Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>XomegaIT Inc</t>
+          <t>OmniTrust Technologies</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, S3, SNS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a18d71c9677d86f</t>
+          <t>https://www.indeed.com/viewjob?jk=861d98ce8ccd9dd9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Software Engineer II - AI/ML OPS Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f42ee3004396e21</t>
+          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Kafka Migration Specialist</t>
+          <t>Senior Software Engineer - onsite Dallas or NYC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, HBase, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10bf1f673e41ef2e</t>
+          <t>https://www.indeed.com/viewjob?jk=1973f445d0cd1f85</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer – Large-Scale IoT (1M+ Devices)</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nuve Controls LLC</t>
+          <t>Field Tech Services LTD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a72eee9e983c45</t>
+          <t>https://www.indeed.com/viewjob?jk=66ccf1b5ae0c7999</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Solutions Architect - AI</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Robots &amp; Pencils</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, API Gateway, IAM, RDS, Scala, DynamoDB</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9e0f4d3981383ee</t>
+          <t>https://www.indeed.com/viewjob?jk=9c635f2175e2d81b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Child Support -Senior Full Stack AI/Java Developer</t>
+          <t>Sr. SQL Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Walton Hills, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=052ff8fd2f21f73c</t>
+          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OmniTrust Technologies</t>
+          <t>Fusion Risk Management</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861d98ce8ccd9dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML OPS Engineer</t>
+          <t>Kafka Microservices Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09190487663b43a8</t>
+          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - onsite Dallas or NYC</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>Ossium Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1973f445d0cd1f85</t>
+          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. SQL Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Walton Hills, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53840554b54acf8</t>
+          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>MLOps Specialist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Field Tech Services LTD</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66ccf1b5ae0c7999</t>
+          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,49 +1441,49 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c635f2175e2d81b</t>
+          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer - Professional</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>VytlOne</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, DynamoDB, Data Modeling, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75a593062a046b0c</t>
+          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kafka Microservices Engineer</t>
+          <t>Senior Kafka Migration Specialist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Kafka, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9657082031b8f8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MLOps Engineer - ML Platform</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fusion Risk Management</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcd62f4513b7126c</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr Engineer - Interactive Compute</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ossium Health</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d316352de1f1e22</t>
+          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Kafka Integration Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa566c97f625b888</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MLOps Specialist</t>
+          <t>Senior Kafka DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,14 +1651,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2068eadbf0fe8b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1672,11 +1672,11 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Google Cloud Platform, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bdf305a59e5377a</t>
+          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>DevOps Engineer (Linux)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>VytlOne</t>
+          <t>Quantifind</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Hadoop, Scala, PostgreSQL, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe8313c04ac16547</t>
+          <t>https://www.indeed.com/viewjob?jk=87617613276c990f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Kafka Migration Specialist</t>
+          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Kafka, Snowflake, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30c54747d746ae84</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Kafka DevOps Engineer</t>
+          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Hadoop, Scala, Kafka, Splunk, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,14 +1791,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bf8d41742bde160</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, PySpark, Scala, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec62477c9e8f1ed</t>
+          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Linux)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Quantifind</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Scala, PostgreSQL, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow</t>
+          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87617613276c990f</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java</t>
+          <t>Senior Software Engineer, Integration Platform</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes</t>
+          <t>AWS, Athena, RDS, Spark, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5096db1f348c8e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=b248613383f89a61</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MLOps Engineer - ML Platform</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>ISHIR</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c93cdb4a040410</t>
+          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Engineer - Interactive Compute</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, NoSQL, MLOps, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,14 +1966,14 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48fd0ce1b8d654bd</t>
+          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Kafka Integration Engineer</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1987,11 +1987,11 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca422cd843ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
+          <t>Kafka Implementation Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,357 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4082f94b884828</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Airflow Infrastructure &amp; Automation Engineer – Silicon Design</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Airflow</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0da910ded33358</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Kafka Schema Registry Engineer</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, NoSQL</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f3bde666c6b8715b</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Credit Karma</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Dataflow, Vertex AI, Spark, Scala, Dask, MLOps, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd459594d11eb54</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Forward Deployed Engineer</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>ISHIR</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc6b92ec89fa5a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=467b235085e3e3c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Azure Databricks Architect-5</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Mahwah, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ddae10e310d8abb2</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Kafka Implementation Consultant</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Databricks, Kafka, NoSQL, CI/CD, Maven</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=5e2d881962d3b864</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Credify Services</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b23147f1037240</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Kafka API Engineer</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03dfa487d865ac88</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Machine Learning Software Engineer</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48d779cadb2f27d6</t>
         </is>
       </c>
     </row>
